--- a/tools/crm-kanri-sheet.xlsx
+++ b/tools/crm-kanri-sheet.xlsx
@@ -22,54 +22,128 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="67">
   <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MEO</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">クライアント管理シート 使い方（</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">対策クライアント管理シート 使い方</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">有料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CRM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ツールを使わずにクライアント管理を行うための無料の自作シートです。</t>
-    </r>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MEO</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・広告・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">制作 共通）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MEO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対策・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告（ディスプレイ／ローカル）・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">META</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP/LP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">制作を組み合わせて契約できるため、</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「顧客一覧」シートではクライアントごとにどのサービスを契約しているかを列で管理します。</t>
   </si>
   <si>
     <t xml:space="preserve">【使い方】</t>
@@ -90,7 +164,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「顧客一覧」シートに新規契約が決まったら</t>
+      <t xml:space="preserve">新規契約が決まったら「顧客一覧」に</t>
     </r>
     <r>
       <rPr>
@@ -126,6 +200,88 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">契約しているサービスの列に「あり」を選択する（プルダウン）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月額運用手数料合計は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MEO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">固定額＋広告運用手数料など、実際に請求する合計額を入力する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   （広告費（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">media</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">費用）はクライアント自身の広告アカウントで支払われるため、ここには含めない）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">契約終了日を入れると「残り日数」が自動計算され、</t>
     </r>
     <r>
@@ -154,51 +310,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ステータス・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GBP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">アクセス権はプルダウンから選択する。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「サマリー」シートでステータス別件数と契約中の合計月額（</t>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「サマリー」シートでサービス別契約件数と</t>
     </r>
     <r>
       <rPr>
@@ -215,98 +335,101 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）が自動集計される。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【運用の目安】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・案件が</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件を超えて対応漏れが増えてきたら、有料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CRM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HubSpot</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無料枠等）への移行を検討してください。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  （</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">docs/meo-tools-comparison.md </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を参照）</t>
+      <t xml:space="preserve">（月次経常収益＝運用手数料の合計）が自動集計される。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【関連ドキュメント】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告のクライアントリンク</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/templates/google-ads-mcc-guide.md</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">META</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告のクライアント連携</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/templates/meta-ads-setup-guide.md</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・料金の考え方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/templates/ryoukinhyou.md</t>
     </r>
   </si>
   <si>
@@ -358,10 +481,169 @@
     <t xml:space="preserve">メールアドレス</t>
   </si>
   <si>
-    <t xml:space="preserve">プラン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月額料金</t>
+    <t xml:space="preserve">MEO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ディスプレイ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ローカル</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">META</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP/LP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">制作</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">月額運用手数料
+合計</t>
   </si>
   <si>
     <t xml:space="preserve">契約開始日</t>
@@ -376,27 +658,7 @@
     <t xml:space="preserve">ステータス</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GBP</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">アクセス権</t>
-    </r>
+    <t xml:space="preserve">アカウント連携状況</t>
   </si>
   <si>
     <t xml:space="preserve">次のアクション</t>
@@ -420,19 +682,59 @@
     <t xml:space="preserve">tanaka@example.com</t>
   </si>
   <si>
-    <t xml:space="preserve">スタンダード</t>
+    <t xml:space="preserve">あり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">なし</t>
   </si>
   <si>
     <t xml:space="preserve">契約中</t>
   </si>
   <si>
-    <t xml:space="preserve">あり</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GBP:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">連携済 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ MCC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リンク済</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">月次レポート送付</t>
   </si>
   <si>
-    <t xml:space="preserve">口コミ返信を毎週実施</t>
+    <t xml:space="preserve">広告はディスプレイのみ、バナーは自社制作</t>
   </si>
   <si>
     <t xml:space="preserve">【サンプル）新宿店】</t>
@@ -450,24 +752,61 @@
     <t xml:space="preserve">sato@example.com</t>
   </si>
   <si>
-    <t xml:space="preserve">ライト</t>
-  </si>
-  <si>
     <t xml:space="preserve">商談中</t>
   </si>
   <si>
-    <t xml:space="preserve">なし</t>
+    <t xml:space="preserve">未連携</t>
   </si>
   <si>
     <t xml:space="preserve">見積り再送</t>
   </si>
   <si>
-    <t xml:space="preserve">初回ヒアリング済み</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">META</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告に興味、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pixel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未設置</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">クライアント状況サマリー</t>
   </si>
   <si>
+    <t xml:space="preserve">■ ステータス別件数</t>
+  </si>
+  <si>
     <t xml:space="preserve">商談中の件数</t>
   </si>
   <si>
@@ -480,6 +819,140 @@
     <t xml:space="preserve">解約の件数</t>
   </si>
   <si>
+    <t xml:space="preserve">■ サービス別 契約中の件数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ディスプレイ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ローカル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">META</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP/LP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">制作</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 収益・更新アラート</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -503,7 +976,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
+      <t xml:space="preserve">＝運用手数料合計）</t>
     </r>
   </si>
   <si>
@@ -532,11 +1005,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="#,##0\円"/>
+    <numFmt numFmtId="165" formatCode="#,##0\円"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,15 +1035,15 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -608,6 +1081,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
@@ -682,7 +1161,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -723,6 +1202,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -731,7 +1214,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -739,11 +1226,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -756,7 +1243,14 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E7D4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -808,7 +1302,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFC6E7D4"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1016,7 +1510,7 @@
     <tabColor rgb="FF1F7A5C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
@@ -1031,20 +1525,20 @@
       <c r="A2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1063,22 +1557,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="10" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1612,7 @@
     <tabColor rgb="FF1F7A5C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1106,59 +1620,74 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="L1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1166,47 +1695,59 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M2" s="9" t="n">
+        <v>46174</v>
+      </c>
+      <c r="N2" s="9" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O2" s="10" t="n">
+        <f aca="true">IF(N2="","",N2-TODAY())</f>
         <v>27</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>46174</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>46265</v>
-      </c>
-      <c r="K2" s="9" t="n">
-        <f aca="true">IF(J2="","",J2-TODAY())</f>
-        <v>27</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>34</v>
+      <c r="P2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1214,786 +1755,1063 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M3" s="9" t="n">
         <v>46143</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="N3" s="9" t="n">
         <v>46234</v>
       </c>
-      <c r="K3" s="9" t="n">
-        <f aca="true">IF(J3="","",J3-TODAY())</f>
+      <c r="O3" s="10" t="n">
+        <f aca="true">IF(N3="","",N3-TODAY())</f>
         <v>-4</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>44</v>
+      <c r="P3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
-      <c r="K4" s="10" t="str">
-        <f aca="true">IF(J4="","",J4-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="11" t="str">
+        <f aca="true">IF(N4="","",N4-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
-      <c r="K5" s="10" t="str">
-        <f aca="true">IF(J5="","",J5-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="11" t="str">
+        <f aca="true">IF(N5="","",N5-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
-      <c r="K6" s="10" t="str">
-        <f aca="true">IF(J6="","",J6-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="11" t="str">
+        <f aca="true">IF(N6="","",N6-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
-      <c r="K7" s="10" t="str">
-        <f aca="true">IF(J7="","",J7-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="11" t="str">
+        <f aca="true">IF(N7="","",N7-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
-      <c r="K8" s="10" t="str">
-        <f aca="true">IF(J8="","",J8-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="11" t="str">
+        <f aca="true">IF(N8="","",N8-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
-      <c r="K9" s="10" t="str">
-        <f aca="true">IF(J9="","",J9-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="11" t="str">
+        <f aca="true">IF(N9="","",N9-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
-      <c r="K10" s="10" t="str">
-        <f aca="true">IF(J10="","",J10-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="11" t="str">
+        <f aca="true">IF(N10="","",N10-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
-      <c r="K11" s="10" t="str">
-        <f aca="true">IF(J11="","",J11-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="11" t="str">
+        <f aca="true">IF(N11="","",N11-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
-      <c r="K12" s="10" t="str">
-        <f aca="true">IF(J12="","",J12-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="11" t="str">
+        <f aca="true">IF(N12="","",N12-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
-      <c r="K13" s="10" t="str">
-        <f aca="true">IF(J13="","",J13-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="11" t="str">
+        <f aca="true">IF(N13="","",N13-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
-      <c r="K14" s="10" t="str">
-        <f aca="true">IF(J14="","",J14-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="11" t="str">
+        <f aca="true">IF(N14="","",N14-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
-      <c r="K15" s="10" t="str">
-        <f aca="true">IF(J15="","",J15-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="11" t="str">
+        <f aca="true">IF(N15="","",N15-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
-      <c r="K16" s="10" t="str">
-        <f aca="true">IF(J16="","",J16-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="11" t="str">
+        <f aca="true">IF(N16="","",N16-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
-      <c r="K17" s="10" t="str">
-        <f aca="true">IF(J17="","",J17-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="11" t="str">
+        <f aca="true">IF(N17="","",N17-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
-      <c r="K18" s="10" t="str">
-        <f aca="true">IF(J18="","",J18-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="11" t="str">
+        <f aca="true">IF(N18="","",N18-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
-      <c r="K19" s="10" t="str">
-        <f aca="true">IF(J19="","",J19-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="11" t="str">
+        <f aca="true">IF(N19="","",N19-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
-      <c r="K20" s="10" t="str">
-        <f aca="true">IF(J20="","",J20-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="11" t="str">
+        <f aca="true">IF(N20="","",N20-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-      <c r="K21" s="10" t="str">
-        <f aca="true">IF(J21="","",J21-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="11" t="str">
+        <f aca="true">IF(N21="","",N21-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
-      <c r="K22" s="10" t="str">
-        <f aca="true">IF(J22="","",J22-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="11" t="str">
+        <f aca="true">IF(N22="","",N22-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
-      <c r="K23" s="10" t="str">
-        <f aca="true">IF(J23="","",J23-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="11" t="str">
+        <f aca="true">IF(N23="","",N23-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
-      <c r="K24" s="10" t="str">
-        <f aca="true">IF(J24="","",J24-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="11" t="str">
+        <f aca="true">IF(N24="","",N24-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
-      <c r="K25" s="10" t="str">
-        <f aca="true">IF(J25="","",J25-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="11" t="str">
+        <f aca="true">IF(N25="","",N25-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
-      <c r="K26" s="10" t="str">
-        <f aca="true">IF(J26="","",J26-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="11" t="str">
+        <f aca="true">IF(N26="","",N26-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
-      <c r="K27" s="10" t="str">
-        <f aca="true">IF(J27="","",J27-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="11" t="str">
+        <f aca="true">IF(N27="","",N27-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
-      <c r="K28" s="10" t="str">
-        <f aca="true">IF(J28="","",J28-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="11" t="str">
+        <f aca="true">IF(N28="","",N28-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
-      <c r="K29" s="10" t="str">
-        <f aca="true">IF(J29="","",J29-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="11" t="str">
+        <f aca="true">IF(N29="","",N29-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
-      <c r="K30" s="10" t="str">
-        <f aca="true">IF(J30="","",J30-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="11" t="str">
+        <f aca="true">IF(N30="","",N30-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
-      <c r="K31" s="10" t="str">
-        <f aca="true">IF(J31="","",J31-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="11" t="str">
+        <f aca="true">IF(N31="","",N31-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
-      <c r="K32" s="10" t="str">
-        <f aca="true">IF(J32="","",J32-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="11" t="str">
+        <f aca="true">IF(N32="","",N32-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
-      <c r="K33" s="10" t="str">
-        <f aca="true">IF(J33="","",J33-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="11" t="str">
+        <f aca="true">IF(N33="","",N33-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
-      <c r="K34" s="10" t="str">
-        <f aca="true">IF(J34="","",J34-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="11" t="str">
+        <f aca="true">IF(N34="","",N34-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
-      <c r="K35" s="10" t="str">
-        <f aca="true">IF(J35="","",J35-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="11" t="str">
+        <f aca="true">IF(N35="","",N35-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
-      <c r="K36" s="10" t="str">
-        <f aca="true">IF(J36="","",J36-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="11" t="str">
+        <f aca="true">IF(N36="","",N36-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
-      <c r="K37" s="10" t="str">
-        <f aca="true">IF(J37="","",J37-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="11" t="str">
+        <f aca="true">IF(N37="","",N37-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
-      <c r="K38" s="10" t="str">
-        <f aca="true">IF(J38="","",J38-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="11" t="str">
+        <f aca="true">IF(N38="","",N38-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
-      <c r="K39" s="10" t="str">
-        <f aca="true">IF(J39="","",J39-TODAY())</f>
-        <v/>
-      </c>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="11" t="str">
+        <f aca="true">IF(N39="","",N39-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="11" t="str">
+        <f aca="true">IF(N40="","",N40-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="11" t="str">
+        <f aca="true">IF(N41="","",N41-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="11" t="str">
+        <f aca="true">IF(N42="","",N42-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="11" t="str">
+        <f aca="true">IF(N43="","",N43-TODAY())</f>
+        <v/>
+      </c>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G2:G200">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"あり"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H200">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"あり"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I200">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"あり"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J200">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"あり"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K2:K200">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"あり"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O200">
+    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="8" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
       <formula>30</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L200" type="list">
-      <formula1>"商談中,契約中,休止,解約"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:K200" type="list">
+      <formula1>"あり,なし"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M200" type="list">
-      <formula1>"あり,なし"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P200" type="list">
+      <formula1>"商談中,契約中,休止,解約"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -2013,69 +2831,129 @@
     <tabColor rgb="FF1F7A5C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>45</v>
+      <c r="A1" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="14" t="n">
-        <f aca="false">COUNTIF(顧客一覧!L:L,"商談中")</f>
+      <c r="A3" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="16" t="n">
+        <f aca="false">COUNTIF(顧客一覧!P:P,"商談中")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="14" t="n">
-        <f aca="false">COUNTIF(顧客一覧!L:L,"契約中")</f>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <f aca="false">COUNTIF(顧客一覧!P:P,"契約中")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="14" t="n">
-        <f aca="false">COUNTIF(顧客一覧!L:L,"休止")</f>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <f aca="false">COUNTIF(顧客一覧!P:P,"休止")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <f aca="false">COUNTIF(顧客一覧!L:L,"解約")</f>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <f aca="false">COUNTIF(顧客一覧!P:P,"解約")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="15" t="n">
-        <f aca="false">SUMIF(顧客一覧!L:L,"契約中",顧客一覧!H:H)</f>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="14" t="n">
-        <f aca="false">COUNTIFS(顧客一覧!L:L,"契約中",顧客一覧!K:K,"&gt;=0",顧客一覧!K:K,"&lt;=30")</f>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <f aca="false">COUNTIFS(顧客一覧!G:G,"あり",顧客一覧!P:P,"契約中")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">COUNTIFS(顧客一覧!H:H,"あり",顧客一覧!P:P,"契約中")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <f aca="false">COUNTIFS(顧客一覧!I:I,"あり",顧客一覧!P:P,"契約中")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <f aca="false">COUNTIFS(顧客一覧!J:J,"あり",顧客一覧!P:P,"契約中")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <f aca="false">COUNTIFS(顧客一覧!K:K,"あり",顧客一覧!P:P,"契約中")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="17" t="n">
+        <f aca="false">SUMIF(顧客一覧!P:P,"契約中",顧客一覧!L:L)</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="16" t="n">
+        <f aca="false">COUNTIFS(顧客一覧!P:P,"契約中",顧客一覧!O:O,"&gt;=0",顧客一覧!O:O,"&lt;=30")</f>
         <v>1</v>
       </c>
     </row>
